--- a/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 8,09</t>
+          <t>-11,96; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,04; -4,87</t>
+          <t>-22,63; -3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 10,1</t>
+          <t>-19,26; 10,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 13,15</t>
+          <t>-7,45; 13,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 12,88</t>
+          <t>-7,92; 12,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 1,04</t>
+          <t>-16,98; 2,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 7,9</t>
+          <t>-6,37; 8,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 2,12</t>
+          <t>-12,36; 2,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 2,24</t>
+          <t>-15,96; 0,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 45,48</t>
+          <t>-44,11; 43,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,26; -21,2</t>
+          <t>-84,03; -13,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 62,13</t>
+          <t>-76,7; 71,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 123,69</t>
+          <t>-35,44; 125,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 109,89</t>
+          <t>-40,13; 106,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,74; 16,6</t>
+          <t>-85,7; 23,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 49,99</t>
+          <t>-28,61; 51,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 13,26</t>
+          <t>-54,28; 17,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,27; 20,38</t>
+          <t>-75,01; 5,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,44</t>
+          <t>-7,12; 1,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -0,32</t>
+          <t>-8,64; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 15,38</t>
+          <t>-7,62; 13,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 3,59</t>
+          <t>-4,2; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 2,05</t>
+          <t>-4,87; 2,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 8,36</t>
+          <t>-3,23; 7,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,44</t>
+          <t>-4,26; 1,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,04</t>
+          <t>-5,51; 0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 9,2</t>
+          <t>-3,98; 7,94</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 8,11</t>
+          <t>-32,43; 10,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -1,08</t>
+          <t>-40,46; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 90,96</t>
+          <t>-37,78; 75,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 28,43</t>
+          <t>-25,13; 27,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 16,1</t>
+          <t>-29,84; 18,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 64,79</t>
+          <t>-21,32; 61,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 9,89</t>
+          <t>-23,99; 8,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 0,42</t>
+          <t>-30,28; 1,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 58,28</t>
+          <t>-22,81; 51,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 11,19</t>
+          <t>-1,5; 11,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 6,49</t>
+          <t>-4,7; 7,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 10,65</t>
+          <t>-1,14; 11,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 0,16</t>
+          <t>-10,99; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 3,62</t>
+          <t>-7,88; 4,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 6,58</t>
+          <t>-7,28; 5,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,93</t>
+          <t>-5,0; 3,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 3,55</t>
+          <t>-4,65; 3,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,11</t>
+          <t>-2,33; 6,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 138,93</t>
+          <t>-15,12; 134,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 88,56</t>
+          <t>-37,69; 96,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 138,15</t>
+          <t>-10,36; 148,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 2,49</t>
+          <t>-68,42; 2,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 40,07</t>
+          <t>-48,25; 51,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 66,79</t>
+          <t>-46,34; 59,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 42,94</t>
+          <t>-35,84; 38,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 36,85</t>
+          <t>-33,91; 41,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 66,15</t>
+          <t>-18,06; 64,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,52</t>
+          <t>-4,03; 2,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,84</t>
+          <t>-6,83; -0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,51</t>
+          <t>-5,28; 11,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,05</t>
+          <t>-4,1; 1,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,62</t>
+          <t>-4,22; 1,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,3</t>
+          <t>-3,8; 4,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,29</t>
+          <t>-3,13; 1,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; -0,35</t>
+          <t>-4,89; -0,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 5,62</t>
+          <t>-3,34; 5,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 15,76</t>
+          <t>-21,07; 16,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -5,21</t>
+          <t>-36,26; -5,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 83,76</t>
+          <t>-29,13; 73,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 16,31</t>
+          <t>-25,86; 13,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 13,34</t>
+          <t>-26,72; 13,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 43,95</t>
+          <t>-25,34; 33,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 8,98</t>
+          <t>-18,55; 10,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,03; -2,23</t>
+          <t>-28,88; -3,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 35,76</t>
+          <t>-20,58; 35,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 7,65</t>
+          <t>-12,58; 7,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -3,65</t>
+          <t>-22,18; -3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 10,7</t>
+          <t>-19,34; 10,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 13,61</t>
+          <t>-6,69; 13,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 12,28</t>
+          <t>-8,38; 12,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 2,08</t>
+          <t>-16,79; 1,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 8,05</t>
+          <t>-6,11; 7,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 2,44</t>
+          <t>-11,89; 2,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 0,48</t>
+          <t>-15,42; 1,16</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 43,41</t>
+          <t>-44,23; 42,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,03; -13,39</t>
+          <t>-83,34; -13,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 71,75</t>
+          <t>-76,18; 57,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 125,15</t>
+          <t>-33,73; 131,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 106,69</t>
+          <t>-40,51; 110,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,7; 23,96</t>
+          <t>-86,72; 21,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 51,2</t>
+          <t>-26,93; 51,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 17,49</t>
+          <t>-53,57; 14,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,01; 5,73</t>
+          <t>-72,48; 12,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,72</t>
+          <t>-6,84; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 0,24</t>
+          <t>-8,47; 0,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 13,59</t>
+          <t>-7,7; 15,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,36</t>
+          <t>-3,99; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,25</t>
+          <t>-5,15; 2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,91</t>
+          <t>-3,51; 8,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,36</t>
+          <t>-4,31; 1,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,19</t>
+          <t>-5,45; -0,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 7,94</t>
+          <t>-3,83; 9,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 10,3</t>
+          <t>-32,74; 8,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 1,49</t>
+          <t>-39,82; 1,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 75,68</t>
+          <t>-37,65; 84,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 27,32</t>
+          <t>-24,88; 29,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 18,99</t>
+          <t>-33,19; 17,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 61,71</t>
+          <t>-22,57; 63,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 8,77</t>
+          <t>-23,55; 9,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 1,31</t>
+          <t>-30,41; -0,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 51,81</t>
+          <t>-22,28; 60,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 11,03</t>
+          <t>-1,54; 10,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 7,1</t>
+          <t>-4,29; 6,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 11,16</t>
+          <t>-1,43; 11,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 0,12</t>
+          <t>-12,25; -0,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 4,59</t>
+          <t>-8,56; 3,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,79</t>
+          <t>-7,09; 5,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,56</t>
+          <t>-4,86; 3,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,71</t>
+          <t>-4,45; 3,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,54</t>
+          <t>-2,76; 5,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 134,27</t>
+          <t>-12,95; 144,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 96,43</t>
+          <t>-34,89; 95,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 148,99</t>
+          <t>-12,87; 146,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 2,35</t>
+          <t>-73,4; -3,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 51,41</t>
+          <t>-51,09; 36,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 59,19</t>
+          <t>-44,77; 55,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 38,05</t>
+          <t>-34,57; 42,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 41,21</t>
+          <t>-32,82; 41,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 64,52</t>
+          <t>-20,93; 59,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,6</t>
+          <t>-4,01; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,91</t>
+          <t>-7,21; -0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 11,61</t>
+          <t>-5,16; 10,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,77</t>
+          <t>-3,98; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,63</t>
+          <t>-4,51; 1,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,43</t>
+          <t>-3,78; 5,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,61</t>
+          <t>-3,2; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,42</t>
+          <t>-4,89; -0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,41</t>
+          <t>-3,29; 5,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 16,09</t>
+          <t>-20,73; 19,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -5,29</t>
+          <t>-37,41; -2,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 73,73</t>
+          <t>-28,38; 72,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 13,87</t>
+          <t>-25,88; 16,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 13,63</t>
+          <t>-28,22; 11,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 33,52</t>
+          <t>-24,75; 38,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 10,89</t>
+          <t>-18,89; 8,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -3,0</t>
+          <t>-28,99; -3,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 35,14</t>
+          <t>-19,99; 37,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-9,07</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-13,49</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,25</t>
+          <t>-12,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,72</t>
+          <t>-10,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,67</t>
+          <t>-5,57; 13,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -3,21</t>
+          <t>-6,73; 12,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 10,02</t>
+          <t>-17,46; 0,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 13,75</t>
+          <t>-12,45; 8,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 12,81</t>
+          <t>-23,04; -4,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 1,26</t>
+          <t>-21,87; -2,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,71</t>
+          <t>-6,05; 7,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 2,21</t>
+          <t>-11,56; 2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 1,16</t>
+          <t>-17,59; -4,35</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-57,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-8,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-60,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-38,38%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-52,52%</t>
+          <t>-55,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-45,41%</t>
+          <t>-57,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 42,31</t>
+          <t>-28,09; 123,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,34; -13,91</t>
+          <t>-33,81; 109,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 57,0</t>
+          <t>-87,72; 17,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 131,3</t>
+          <t>-46,19; 45,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 110,94</t>
+          <t>-84,26; -21,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 21,46</t>
+          <t>-82,03; -7,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 51,16</t>
+          <t>-27,13; 49,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 14,61</t>
+          <t>-52,92; 13,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 12,58</t>
+          <t>-79,36; -21,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,5</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-1,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,66</t>
+          <t>-3,74; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 0,3</t>
+          <t>-5,58; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 15,07</t>
+          <t>-3,2; 7,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,76</t>
+          <t>-7,03; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 2,13</t>
+          <t>-9,17; -0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,54</t>
+          <t>-9,34; -0,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,4</t>
+          <t>-4,29; 1,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,03</t>
+          <t>-5,69; 0,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 9,41</t>
+          <t>-5,09; 2,0</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,41%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-14,61%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-23,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,41%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>-26,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>-11,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 8,58</t>
+          <t>-24,18; 28,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 1,68</t>
+          <t>-33,65; 16,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 84,18</t>
+          <t>-21,14; 56,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 29,55</t>
+          <t>-33,66; 8,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 17,14</t>
+          <t>-41,41; -1,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 63,5</t>
+          <t>-44,3; -3,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 9,02</t>
+          <t>-23,3; 9,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,41; -0,11</t>
+          <t>-31,13; 0,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 60,5</t>
+          <t>-27,82; 12,76</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,43</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,81</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 10,87</t>
+          <t>-11,25; 0,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,55</t>
+          <t>-8,75; 3,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 11,26</t>
+          <t>-7,07; 5,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -0,57</t>
+          <t>-1,63; 11,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 3,73</t>
+          <t>-4,6; 6,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,5</t>
+          <t>-1,63; 10,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,83</t>
+          <t>-4,88; 3,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,83</t>
+          <t>-4,73; 3,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,95</t>
+          <t>-3,02; 6,17</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-44,85%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-16,12%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-10,89%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>46,91%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-44,85%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-16,12%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,17%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 144,68</t>
+          <t>-70,54; 2,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 95,46</t>
+          <t>-49,86; 40,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 146,01</t>
+          <t>-45,36; 60,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,4; -3,08</t>
+          <t>-17,81; 138,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 36,98</t>
+          <t>-37,6; 88,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 55,26</t>
+          <t>-15,1; 141,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 42,02</t>
+          <t>-36,86; 42,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 41,08</t>
+          <t>-34,3; 36,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 59,56</t>
+          <t>-22,49; 66,98</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-3,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-1,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,06</t>
+          <t>-3,61; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,38</t>
+          <t>-3,96; 1,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 10,81</t>
+          <t>-3,71; 4,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,13</t>
+          <t>-4,18; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,54</t>
+          <t>-7,21; -0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,09</t>
+          <t>-7,28; -0,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,26</t>
+          <t>-3,13; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,56</t>
+          <t>-4,77; -0,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,71</t>
+          <t>-4,44; 0,65</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-7,38%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9,03%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-3,4%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-4,47%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-1,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,38%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-9,03%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,12%</t>
+          <t>-19,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,8%</t>
+          <t>-12,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 19,6</t>
+          <t>-23,41; 16,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -2,12</t>
+          <t>-26,13; 13,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 72,64</t>
+          <t>-24,92; 35,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 16,5</t>
+          <t>-22,17; 15,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 11,8</t>
+          <t>-38,69; -5,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 38,15</t>
+          <t>-36,73; 0,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 8,54</t>
+          <t>-18,67; 8,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,99; -3,49</t>
+          <t>-28,03; -2,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 37,24</t>
+          <t>-26,44; 4,34</t>
         </is>
       </c>
     </row>
